--- a/Output Format.xlsx
+++ b/Output Format.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y17"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
@@ -1904,6 +1904,488 @@
       <c r="Y17" s="5" t="n">
         <v>-0.3774104683195592</v>
       </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Johnny's Fine Foods Inc.</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Promotional Event</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EXTRAORDINAIRE</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>34</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>46023</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>46203</v>
+      </c>
+      <c r="G18" t="n">
+        <v>286</v>
+      </c>
+      <c r="H18" t="n">
+        <v>16</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>0.05594405594405594</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1484</v>
+      </c>
+      <c r="M18" t="n">
+        <v>16</v>
+      </c>
+      <c r="N18" t="n">
+        <v>10</v>
+      </c>
+      <c r="O18" t="n">
+        <v>9</v>
+      </c>
+      <c r="P18" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>21</v>
+      </c>
+      <c r="R18" t="n">
+        <v>160</v>
+      </c>
+      <c r="S18" s="5" t="n">
+        <v>7.421052631578948</v>
+      </c>
+      <c r="T18" s="5" t="n">
+        <v>6.619047619047618</v>
+      </c>
+      <c r="U18" t="n">
+        <v>19</v>
+      </c>
+      <c r="V18" t="n">
+        <v>21</v>
+      </c>
+      <c r="W18" t="n">
+        <v>137</v>
+      </c>
+      <c r="X18" s="5" t="n">
+        <v>6.210526315789474</v>
+      </c>
+      <c r="Y18" s="5" t="n">
+        <v>5.523809523809524</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Ferolito Vultaggio &amp; Sons</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Arizona tea</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EXCEL</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>46028</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>46083</v>
+      </c>
+      <c r="G19" t="n">
+        <v>166</v>
+      </c>
+      <c r="H19" t="n">
+        <v>28</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>0.1686746987951807</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K19" t="n">
+        <v>25</v>
+      </c>
+      <c r="L19" t="n">
+        <v>20.52</v>
+      </c>
+      <c r="M19" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="N19" t="n">
+        <v>28</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3</v>
+      </c>
+      <c r="P19" t="n">
+        <v>766</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>621</v>
+      </c>
+      <c r="R19" t="n">
+        <v>710</v>
+      </c>
+      <c r="S19" s="5" t="n">
+        <v>-0.0731070496083551</v>
+      </c>
+      <c r="T19" s="5" t="n">
+        <v>0.143317230273752</v>
+      </c>
+      <c r="U19" t="n">
+        <v>364</v>
+      </c>
+      <c r="V19" t="n">
+        <v>328</v>
+      </c>
+      <c r="W19" t="n">
+        <v>371</v>
+      </c>
+      <c r="X19" s="5" t="n">
+        <v>0.01923076923076923</v>
+      </c>
+      <c r="Y19" s="5" t="n">
+        <v>0.1310975609756098</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Borden, Inc.</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Meadow Gold Cottage Cheese</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EXCEL</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>46056</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>46111</v>
+      </c>
+      <c r="G20" t="n">
+        <v>224</v>
+      </c>
+      <c r="H20" t="n">
+        <v>13</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>0.05803571428571429</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K20" t="n">
+        <v>25</v>
+      </c>
+      <c r="L20" t="n">
+        <v>19.67</v>
+      </c>
+      <c r="M20" t="n">
+        <v>5.329999999999998</v>
+      </c>
+      <c r="N20" t="n">
+        <v>13</v>
+      </c>
+      <c r="O20" t="n">
+        <v>5</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2236</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1821</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1454</v>
+      </c>
+      <c r="S20" s="5" t="n">
+        <v>-0.3497316636851521</v>
+      </c>
+      <c r="T20" s="5" t="n">
+        <v>-0.2015376166941241</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1839</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1530</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1282</v>
+      </c>
+      <c r="X20" s="5" t="n">
+        <v>-0.3028820010875476</v>
+      </c>
+      <c r="Y20" s="5" t="n">
+        <v>-0.1620915032679738</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CG Roxane, LLC</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Crystal Geyser Spring Water</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EXCEL</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>46063</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>46118</v>
+      </c>
+      <c r="G21" t="n">
+        <v>180</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>0.02222222222222222</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K21" t="n">
+        <v>25</v>
+      </c>
+      <c r="L21" t="n">
+        <v>23.76</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.239999999999998</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>16</v>
+      </c>
+      <c r="S21" s="5" t="inlineStr"/>
+      <c r="T21" s="5" t="inlineStr"/>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>8</v>
+      </c>
+      <c r="X21" s="5" t="inlineStr"/>
+      <c r="Y21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Cache Valley Dairy Association</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Cache Valley Cheese</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EXCEL</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>5</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>46063</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>46118</v>
+      </c>
+      <c r="G22" t="n">
+        <v>320</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>0.009375</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K22" t="n">
+        <v>25</v>
+      </c>
+      <c r="L22" t="n">
+        <v>22.15</v>
+      </c>
+      <c r="M22" t="n">
+        <v>2.850000000000001</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2</v>
+      </c>
+      <c r="P22" t="n">
+        <v>881</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1429</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1388</v>
+      </c>
+      <c r="S22" s="5" t="n">
+        <v>0.5754824063564131</v>
+      </c>
+      <c r="T22" s="5" t="n">
+        <v>-0.02869139258222533</v>
+      </c>
+      <c r="U22" t="n">
+        <v>678</v>
+      </c>
+      <c r="V22" t="n">
+        <v>952</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1023</v>
+      </c>
+      <c r="X22" s="5" t="n">
+        <v>0.5088495575221239</v>
+      </c>
+      <c r="Y22" s="5" t="n">
+        <v>0.07457983193277311</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Alanric Food Distributors, Inc.</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Cento tomatoe paste and purees</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EXCEL</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>46069</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>46152</v>
+      </c>
+      <c r="G23" t="n">
+        <v>28</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K23" t="n">
+        <v>25</v>
+      </c>
+      <c r="L23" t="n">
+        <v>25</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>38</v>
+      </c>
+      <c r="S23" s="5" t="inlineStr"/>
+      <c r="T23" s="5" t="inlineStr"/>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>31</v>
+      </c>
+      <c r="X23" s="5" t="inlineStr"/>
+      <c r="Y23" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
